--- a/dados_auxiliares/emails_relatorio.xlsx
+++ b/dados_auxiliares/emails_relatorio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>nome</t>
   </si>
@@ -40,6 +40,15 @@
   </si>
   <si>
     <t>nsfaita@prefeitura.sp.gov.br</t>
+  </si>
+  <si>
+    <t>Alan Assis Martins Munhoz</t>
+  </si>
+  <si>
+    <t>Diretor I</t>
+  </si>
+  <si>
+    <t>ammunhoz@PREFEITURA.SP.GOV.BR</t>
   </si>
 </sst>
 </file>
@@ -103,8 +112,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:D2" totalsRowShown="0">
-  <autoFilter ref="A1:D2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:D3" totalsRowShown="0">
+  <autoFilter ref="A1:D3"/>
   <tableColumns count="4">
     <tableColumn id="1" name="nome"/>
     <tableColumn id="2" name="cargo"/>
@@ -402,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -433,14 +442,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
